--- a/human_resources_forms/048_sales_performance_reflection_form--human_resources_forms.xlsx
+++ b/human_resources_forms/048_sales_performance_reflection_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sales_performance_reflection_form</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,20 +538,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>reflection_time</t>
+          <t>reflection_activities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reflection_time</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Reflect on your sales activities this period</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please reflect on your sales activities</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,43 +565,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>sales_num</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What were the sales numbers for this period?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide the numbers</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>sales_num2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Sales Num2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide the numbers</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +619,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>sales_strategy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your current sales strategy?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your current sales strategy</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +646,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>sales_strategy2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Sales Strategy2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your current sales strategy</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +673,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>sales_team_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How do you manage your sales team?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide your approach to sales team management</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,21 +700,322 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sales_manager</t>
+          <t>feedback_and_suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sales_manager</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have any feedback or suggestions for improvement?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide any feedback or suggestions</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sales_manager_role</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Are you a sales manager?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please answer yes or no</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sales_manager_responsibilities</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What are your responsibilities as a sales manager?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide your responsibilities</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sales_manager_feedback</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any feedback for your sales manager?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide feedback</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sales_performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How would you rate your sales performance this period?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please rate on a scale of 1-5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>feedback_and_suggestions2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Feedback And Suggestions2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any feedback or suggestions</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sales_manager_feedback2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sales Manager Feedback2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide feedback</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sales_manager_responsibilities2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sales Manager Responsibilities2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide your responsibilities</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sales_manager_role2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sales Manager Role2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please answer yes or no</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sales_performance_improvement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Do you have any suggestions for improving your sales performance?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide suggestions</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sales_manager_responsibilities3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sales Manager Responsibilities3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please provide your responsibilities</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sales_performance_review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Would you like to receive a performance review?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please answer yes or no</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,10 +1032,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -735,7 +1060,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_manager_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,7 +1077,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_manager_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,7 +1094,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_manager_role2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -786,7 +1111,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_manager_role2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -803,7 +1128,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_performance_review_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -820,7 +1145,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sales_manager_choices</t>
+          <t>sales_performance_review_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,108 +1154,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sales_manager_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
